--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrWtSpotex001.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrWtSpotex001.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ideaworkspaces\ZGBS-CP-dev\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13590" windowHeight="5985"/>
   </bookViews>
@@ -76,7 +81,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>交易完成度（%）</t>
+    <t>交易完成度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -425,7 +430,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
